--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,82 +55,52 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>В5786КН</t>
+  </si>
+  <si>
+    <t>В8990ВР</t>
   </si>
   <si>
     <t>В0843ТМ</t>
   </si>
   <si>
-    <t>В8990ВР</t>
-  </si>
-  <si>
-    <t>В5786КН</t>
+    <t>78970155027720741</t>
+  </si>
+  <si>
+    <t>78970155027720766</t>
   </si>
   <si>
     <t>78970155027720758</t>
   </si>
   <si>
-    <t>78970155027720766</t>
-  </si>
-  <si>
-    <t>78970155027720741</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:20:00</t>
-  </si>
-  <si>
-    <t>10:28:00</t>
-  </si>
-  <si>
-    <t>14:58:00</t>
-  </si>
-  <si>
-    <t>12:53:00</t>
-  </si>
-  <si>
-    <t>14:04:00</t>
-  </si>
-  <si>
-    <t>14:03:00</t>
-  </si>
-  <si>
-    <t>09:57:00</t>
-  </si>
-  <si>
-    <t>3236510485 3236510485</t>
-  </si>
-  <si>
-    <t>3236654568 3236654568</t>
-  </si>
-  <si>
-    <t>3236715898 3236715898</t>
-  </si>
-  <si>
-    <t>3236922666 3236922666</t>
-  </si>
-  <si>
-    <t>3236958600 3236958600</t>
-  </si>
-  <si>
-    <t>3237059295 3237059295</t>
-  </si>
-  <si>
-    <t>3237205336 3237205336</t>
-  </si>
-  <si>
-    <t>3237217946 3237217946</t>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>20:29</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -556,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -565,17 +532,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -615,104 +581,95 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H2" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="J2" s="1">
+        <v>32.4</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>309373</v>
+      </c>
+      <c r="M2">
+        <v>250354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>37.38</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H3" s="1">
+        <v>15.9</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="J3" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>24.297</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>24.671</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>119710</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46254</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>34.91</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="1">
-        <v>22.691</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>23.041</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
+      <c r="L3">
+        <v>119140</v>
       </c>
       <c r="M3">
-        <v>118500</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>146820</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -724,83 +681,77 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>36.48</v>
-      </c>
-      <c r="G4" t="s">
+        <v>30.77</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4" s="1">
+        <v>20.308</v>
+      </c>
+      <c r="K4" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I4" s="1">
-        <v>23.712</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
-        <v>24.077</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
+      <c r="L4">
+        <v>119140</v>
       </c>
       <c r="M4">
-        <v>119960</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>146820</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
       <c r="F5">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.59</v>
       </c>
       <c r="H5" s="1">
-        <v>1.55</v>
+        <v>15.9</v>
       </c>
       <c r="I5" s="1">
-        <v>46.5</v>
+        <v>1.62</v>
       </c>
       <c r="J5" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="K5" s="1">
-        <v>47.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
+        <v>16.2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <v>120520</v>
       </c>
       <c r="M5">
-        <v>308945</v>
-      </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>250384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -812,168 +763,156 @@
         <v>22</v>
       </c>
       <c r="F6">
-        <v>31.56</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
+        <v>37.38</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.65</v>
       </c>
       <c r="H6" s="1">
-        <v>0.65</v>
+        <v>24.297</v>
       </c>
       <c r="I6" s="1">
-        <v>20.514</v>
+        <v>0.66</v>
       </c>
       <c r="J6" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K6" s="1">
-        <v>20.83</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
+        <v>24.671</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>120520</v>
       </c>
       <c r="M6">
-        <v>118720</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>250384</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
-        <v>46262</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H7" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J7" s="1">
+        <v>49.2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>308545</v>
+      </c>
+      <c r="M7">
+        <v>300319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>37.39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I7" s="1">
-        <v>24.304</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K7" s="1">
-        <v>24.677</v>
-      </c>
-      <c r="L7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7">
-        <v>120230</v>
-      </c>
-      <c r="N7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3">
-        <v>46265</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
       </c>
       <c r="F8">
-        <v>15.71</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
+        <v>24.6</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.66</v>
       </c>
       <c r="H8" s="1">
-        <v>0.65</v>
+        <v>16.236</v>
       </c>
       <c r="I8" s="1">
-        <v>10.212</v>
+        <v>0.67</v>
       </c>
       <c r="J8" s="1">
+        <v>16.482</v>
+      </c>
+      <c r="K8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>119355</v>
+      </c>
+      <c r="M8">
+        <v>300387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>36.96</v>
+      </c>
+      <c r="G9" s="1">
         <v>0.66</v>
       </c>
-      <c r="K8" s="1">
-        <v>10.369</v>
-      </c>
-      <c r="L8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8">
-        <v>118880</v>
-      </c>
-      <c r="N8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3">
-        <v>46265</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>24</v>
-      </c>
       <c r="H9" s="1">
-        <v>1.58</v>
+        <v>24.394</v>
       </c>
       <c r="I9" s="1">
-        <v>47.4</v>
+        <v>0.67</v>
       </c>
       <c r="J9" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="K9" s="1">
-        <v>48.3</v>
-      </c>
-      <c r="L9" t="s">
-        <v>31</v>
+        <v>24.763</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9">
+        <v>120800</v>
       </c>
       <c r="M9">
-        <v>309222</v>
-      </c>
-      <c r="N9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>256656</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -981,82 +920,82 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:13">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="7">
-        <v>193.43</v>
+        <v>129.71</v>
       </c>
       <c r="C14" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" s="9">
-        <v>0.65</v>
+        <v>0.6547500000000001</v>
       </c>
       <c r="E14" s="7">
-        <v>125.73</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="F14" s="7">
-        <v>127.66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>86.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" s="7">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C15" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="9">
-        <v>1.565</v>
+        <v>1.59857</v>
       </c>
       <c r="E15" s="7">
-        <v>93.90000000000001</v>
+        <v>111.9</v>
       </c>
       <c r="F15" s="7">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="10" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B16" s="11">
-        <v>253.43</v>
+        <v>199.71</v>
       </c>
       <c r="C16" s="12">
         <v>8</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="11">
-        <v>219.63</v>
+        <v>196.83</v>
       </c>
       <c r="F16" s="11">
-        <v>223.36</v>
+        <v>200.22</v>
       </c>
     </row>
   </sheetData>
